--- a/important_mails_2026-04-12.xlsx
+++ b/important_mails_2026-04-12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,71 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+          <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+          <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -540,39 +590,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -593,39 +643,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -649,39 +699,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -696,39 +746,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -742,40 +792,40 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -789,58 +839,6 @@
 - Set the date range from April 15 2026, to May 15 2026, and click Update .
 - Download the file and open it in Excel.
 - Filter the Product details column with Digital services fee adjustment and Taxes on digital services fee adjustment .</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
-On 04/05/26 13:38 PDT, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
- 177.58.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
- Amazon sellers and Amazon Pay merchants can si</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2671,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2688,65 +2686,21 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
+          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
+          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
-Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
-Per vedere i suoi ordini ed effettuare operazioni a essi relative, come per esempio l'emissione di rimborsi, visiti Seller Central al link: http://sellercentral-europe.amazon.com. Maggiori informazioni su come gestire i prodotti, gli ordini e il suo negozio online sono disponibili nelle pagine di aiuto di Seller Central.
-Per contattarci nuovamente riguardo a questo problema utilizzi il modulo di contatto di Seller Central cliccando su questo link:
-https://sellercentral-europe.amazon.com/cu/case-dashboard/view-case?caseID=12317833332
-Se desidera ricevere aiuto da altri venditori, può visitare il nostro Forum per i venditori a questo link: https://sellercentral.amazon.it/forums/
-La preghiamo di non rispondere a questo messaggio. Questa e-mail è stata inviata da un indirizzo che non accetta posta in entrata.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -2759,39 +2713,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -2807,39 +2761,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -2859,39 +2813,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -2910,39 +2864,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -2951,39 +2905,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3009,39 +2963,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3061,40 +3015,40 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -3110,39 +3064,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3162,39 +3116,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -3220,39 +3174,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3268,39 +3222,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3321,39 +3275,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -3367,40 +3321,40 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -3413,6 +3367,58 @@
  Bonjour d’Amazon Services,
  Nous avons débité votre carte bancaire (Visa) pour CDN$ 44.03 pour le règlement du solde de votre compte vendeur.
  Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
+On 04/05/26 13:38 PDT, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
+ 177.58.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+ Amazon sellers and Amazon Pay merchants can si</t>
         </is>
       </c>
     </row>
@@ -4836,21 +4842,65 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
+          <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
+          <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
+Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
+Per vedere i suoi ordini ed effettuare operazioni a essi relative, come per esempio l'emissione di rimborsi, visiti Seller Central al link: http://sellercentral-europe.amazon.com. Maggiori informazioni su come gestire i prodotti, gli ordini e il suo negozio online sono disponibili nelle pagine di aiuto di Seller Central.
+Per contattarci nuovamente riguardo a questo problema utilizzi il modulo di contatto di Seller Central cliccando su questo link:
+https://sellercentral-europe.amazon.com/cu/case-dashboard/view-case?caseID=12317833332
+Se desidera ricevere aiuto da altri venditori, può visitare il nostro Forum per i venditori a questo link: https://sellercentral.amazon.it/forums/
+La preghiamo di non rispondere a questo messaggio. Questa e-mail è stata inviata da un indirizzo che non accetta posta in entrata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -4860,39 +4910,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -4902,39 +4952,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -4964,39 +5014,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5014,39 +5064,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5063,39 +5113,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5111,39 +5161,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5172,39 +5222,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5225,39 +5275,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5272,39 +5322,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5318,40 +5368,40 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5367,39 +5417,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5415,39 +5465,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5463,39 +5513,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5511,40 +5561,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5560,39 +5610,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5610,39 +5660,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5658,39 +5708,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5705,39 +5755,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -5752,39 +5802,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5805,40 +5855,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -5853,39 +5903,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -5906,39 +5956,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -5971,39 +6021,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6019,39 +6069,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6067,39 +6117,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6117,39 +6167,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6166,39 +6216,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -6222,39 +6272,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6269,39 +6319,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6317,39 +6367,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6366,40 +6416,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6415,39 +6465,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -6467,39 +6517,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6520,39 +6570,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6575,39 +6625,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6628,39 +6678,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6684,39 +6734,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6739,39 +6789,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6794,39 +6844,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6848,39 +6898,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6898,39 +6948,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -6960,39 +7010,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7008,39 +7058,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7056,40 +7106,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7108,40 +7158,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,

--- a/important_mails_2026-04-12.xlsx
+++ b/important_mails_2026-04-12.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2612,7 +2612,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2627,21 +2627,1969 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
+          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>RE:[CASE 12317833332] 其他账户问题</t>
+          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
+ Hello,
+ Starting from April 30, 2026, your Fulfilment by Amazon (FBA) inventory that’s been stored over 270 days (aged), stranded over 60 days or unfulfillable over 14 days will be removed from our UK and EU fulfilment centres to free up capacity in our network.
+ If you don’t complete one of the following actions by April 30, 2026, we may automatically dispose, donate, liquidate or return your inventory.
+- For aged inventory (270+ days): Review your at-risk inventory in FBA inventory , then go to Automated fulfillable settings in Seller Central settings and choose a removal option: Disable, return (processing may take up to 90 days) or dispose (liquidation is available for eligible inventory). If you choose Disable, we will not remove your aged inventory.
+- For unfulfillable inventory: Go to Remove unfulfillable inventory and create a removal order.
+- For stranded inventory: Go to Fix stranded inventory and create a removal order or select “Edit automatic action settings” to configure your removal preferences. Note: If you’ve created a return order for FBA inventory in last six months, we’ll att</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
+C2S2 PCP Pallet Limited Time Promotion
+Dear Selling Partner,
+Ready to unlock European growth? Join Customs Clearance and Shipping Service (C2S2) PCP Pallets and get an unbeatable launch package: up to €240 in transportation fee reimbursements per shipment during our Spring Promotion (April 10 - June 30, 2026), PLUS 1 year of free Indirect Representation (IR) worth €200, PLUS your first shipment worth €60 completely free.
+It's the perfect time to start shipping cross-border with confidence. Join for free to the PCP-AVASK Pallet solution today.
+[Enroll now with AVASK](https://go.amazonsellerservices.com/e/229492/jfe-form-SV-cA1EXJ0WHz20OFg/7z2qvf2/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
+- Automatic tracking: No claims process - we track your shipments automatically
+- Check full [terms and conditions here](https://go.amazonsellerservices.com/e/229492/-C2S2-LTL-Q2-Promotion-TCs-pdf/7z2qvf5/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
+Offer Details:
+Pallets per Shipment                               Your Savings
+1-5 pallets    </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>FBA removal and disposal fees to be charged as units are processed</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>96
+ FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
+ Hello,
+ Effective May 1, 2026, Fulfillment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
+ This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
+ No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
+ To review your removal and disposal shipment level charges and when units are removed, go to Transaction view .
+ For more information, go to FBA Removal and Disposal fee updates .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon EU S.à r.l.
+38 avenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>FBA removal and disposal fees to be charged as units are processed</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>96
+ FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
+ Hello,
+ Effective as of May 1, 2026, Fulfilment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time that each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
+ This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
+ No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
+ To review your removal and disposal shipment-level charges and when units are removed, go to Transaction view .
+ For more information, go to FBA removal and disposal fee updates .
+ The Amazon Europe team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon EU S.à</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Update to FBA item package dimensions</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Update to FBA item package dimensions
+ 96
+ Starting May 5, 2026, we'll update the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, France, Italy and Spain stores.
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (pVfzD86piw)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed and shipped your removal
+request (pVfzD86piw) to the address you specified before.
+Return Summary:
+Quantity Requested: 3
+Quantity Successfully Shipped: 3
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being shipped, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-1560397-6680802
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1143494293097040</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (CQhO1/+c38)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-5850124-1743211
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-650912521107592</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
+ votre compte vendeur Amazon</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For details, go to seller Help, and search for “Make a Payment.”
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report.
+ Thank you for selling on Amazon.ca.
+ Amazon Services
+ *****
+ Bonjour d’Amazon Services,
+ Nous avons débité votre carte bancaire (Visa) pour CDN$ 44.65 pour le règlement du solde de votre compte vendeur.
+ Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (kpCypnMqWe)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1188095-0289626
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1372192148348110</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (UvRxALtvwM)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed and shipped your removal
+request (UvRxALtvwM) to the address you specified before.
+Return Summary:
+Quantity Requested: 1
+Quantity Successfully Shipped: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being shipped, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-2770073-9467132
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1178678664727600</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID pVfzD86piw
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on April 5, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-1213863031250684</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Reminder: Please share your feedback on MCF
+Dear Weihai US,
+As a valued Multi-Channel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than March 19.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_et9BAqtoDGCsCB8?Q_CHL=gl&amp;amp;Q_DL=EMD_Z45pcIhoS9Jgg2Y_et9BAqtoDGCsCB8_CGC_gVqjuURBQB4eTq0&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multi-Channel Fulfillment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please vi</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
+On 04/05/26 13:38 PDT, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
+ 177.58.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+ Amazon sellers and Amazon Pay merchants can si</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 04/02/26 15:38 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 23,43.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxi</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon Services
+ 96
+ Review details about your EPR Pay on Behalf reserved amount
+ Hello,
+ Starting 01-04-2026, we'll hold €501.64 from your payments to cover the eco-contribution fees and Extended Producer Responsibility (EPR) Pay on Behalf service fees for sales of products subject to EPR obligations in our Amazon.es - Amazon.fr store in 2025.
+ EPR Pay on Behalf calculates and pays eco-contribution fees for your sales, then debits those amounts from your account. Once fees are charged, any excess reserves will return to your account.
+ Our records show you have products listed in the following EPR categories:
+ - Do-it-yourself (DIY)
+ - Electronical and electrical equipment
+ - Packaging
+ - Sports
+ - Textile
+ - Toys
+ The amount held back is a combination of two fees:
+ Due eco-contribution fees - €299.7
+ EPR Pay on Behalf service fees - €201.94
+ After 01-04-2026, to review your ASIN-level calculations, reserved amount details, and the reporting period for each EPR category, go to the EPR Pay on Behalf dashboard .
+ The reserved amount will be adjusted monthly according to your sales volume. If the reserved amount isn't enough to cover the eco-contributions, we'll charge the additional </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 03/30/26 15:13 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 133.79.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>View your China tax report for October - December 2025</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>96
+ We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
+ Hello,
+ According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
+ We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
+ Download your quarterly report (link active for seven days)
+This report is provided for your reference only, no action is required.
+ Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
+ Download your order-level report (link active for seven days)
+Note: Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
+ We’ll continue to provide you with quarterly updates on data shared with the Chinese tax authority.
+ For more information, go to China tax information reporti</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 03/19/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 74,59.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éxit</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>【请勿回复】
+尊敬的销售合作伙伴，
+《2025/40包装和包装废弃物法规》（PPWR）为所有欧盟国家引入了新要求，旨在使包装更具可持续性、减少废弃物并支持循环经济。相关要求预计于2026年8月12日起正式生效。
+您需要为每个销售包装及包装产品的欧盟成员国，分别获取一个对应国家的EPR包装注册号。包括您已注册“EPR代付服务”的国家。提交有效的包装EPR注册号（ERN）后，您可继续参与EPR代付服务——由我们负责及时完成您在亚马逊店铺销售的环保款项申报、填报及付款。
+【如何完成合规？】
+1. 为简化法国、意大利和西班牙的EPR包装注册流程并协助您完成注册，我们与服务提供商建立了合作，提供具有竞争力的收费方案：
+• 协助您获取法国、意大利和西班牙的包装注册号
+• 代表您担任授权代表（如适用）
+如需 Evat Master/AVASK联系： 请访问 https://sellercentral-europe.amazon.com/gc/epr-compliance/epr-registration-packaging?ref=121_SET_PPWR 根据步骤1提示选择您的服务提供商，通过卖家平台服务中心表单提交您的联系信息。
+注意：填写注册表时，请务必根据提示完整填写您的信息。填写后我们将与服务提供商共享您的业务信息，服务提供商将在72小时内与您联系，提供更多合规服务信息。
+2. 如果您已注册“EPR代付服务”（法国、意大利、西班牙）且拥有有效注册号：您需要将号码上传到亚马逊平台，但上传时您仍然可以选择继续参与代付服务或退出以便自行管理EPR销售申报环保费用。
+如何操作：请访问： https://sellercentral-europe.amazon.com/gc/epr-compliance/epr-registration-packaging?ref=121_SET_PPWR 根据步骤2提示完成选择。
+3. 此外，您也可以通过以下任一途径搜索并选择服务提供商、授权代表完成EPR所有欧盟国家包装法号码注册：
+1) 亚马逊服务商网络：https://spn.globalsellingcommunity.cn/discover
+2) 卖家服务商城： https://sellercentral-europe.amazon.com/service-hub （包装法服务即将上线）。
+更多详细指导，请参考此合规手册：https://m.media-amazon.com/images/G/01/CN_Compliance_Team/PPWR_Compliance_Guidebook.pdf
+如有疑问，请扫码加入亚马逊卖家合规群：
+https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jp</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Address compliance requirements for your listings</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>96
+Action required: Important information about your product listings
+ We are contacting you because you have listed products that require you to submit compliance documents.
+ Product listings are missing required compliance documents
+ Hello,
+ We are contacting you because you have listed products that require you to submit compliance documents. Click on Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
+ Review Compliance Requirements
+ The table below contains a sample of your affected listings. Click on Review Compliance Requirements to see all of your affected listings.
+ SKU ASIN Listing Status WH-PW Kit0806 B0DSM44PRS Removed
+ Why is this happening?
+This requirement helps to ensure that products are compliant with local laws and safe for customers.
+ How do I continue to sell the affected products?
+Click on Review Compliance Requirements to find out more information about the documents you need to provide for each product.
+ Was there an error?
+If you believe that you do not need to su</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Live Q&amp;A on customer feedback with experienced sellers</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+Connect with sellers experienced in customer feedback
+Join us on March 31 for a live Q&amp;A event in the New Seller Community. Experienced Amazon selling partners will answer your customer feedback questions, offering insights from their own journey.
+Before the event, post your toughest questions about managing feedback, buyer-seller messaging, and customer relations.
+[Post your question](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+[An Amazon delivery driver walks next to an Amazon Prime delivery van.](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
+Meet our hosts
+[A checkmark icon]
+Amazon Seller: TVOI50
+Hi, my name is Tish. We’ve been selling on Amazon for 5 years in the Office Furniture category. We are FBM, an authorized re-seller for a major furniture manufacturer and strive to make every transaction a seamless one. If it’s not, our customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0FCDRNTT8, B0D7SKQ6GC
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0D7SKQ6GC, B0FCDRNTT8
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
+We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0D7SKQ6GC, B0FCDRNTT8
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.com/fixyourproducts/drafts
+To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+https://sellercentral.amazon.com/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/20/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FD8VC559
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-1161086478880000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Submit UK import details by 21/05/2026 to avoid shipping
+ restrictions</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit UK import details by 21/05/2026 to avoid shipping restrictions
+ Hello Weihai EU,
+ Your Amazon.co.uk seller account requires Import Entry Numbers (IENs) for shipments to UK fulfilment centres. You must provide these details by 21/05/2026 to continue creating new UK shipments.
+ Why is this happening?
+ We are taking this action because we identified shipments to Amazon UK fulfilment centres without valid Import Entry Numbers (IENs). UK Customs authorities assign these IENs when goods are imported into the UK. As the seller, you must obtain these numbers from your customs declarant, logistics agent or freight forwarder to maintain UK shipping compliance .
+ Where do I enter my Import Entry Numbers (IEN)?
+ To enter the IENs for your applicable shipments:
+- Go to your Shipping Queue and identify shipments received in Amazon UK FCs.
+- Under “Status”, click the “Import details” text. It will open a pop-up, where you can enter the IENs corresponding to the relevant shipment. You must provide a valid IEN.
+- Save your IEN entry.
+ If you would need to update your IEN, you can follow the above steps again.
+ What happens if I don’t submit these details?
+ You have 60 days after first re</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Add products to Amazon.nl for Pan EU eligibility</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Add products to Amazon.nl for Pan EU eligibility 96
+ Complete Pan EU enrollment: Add NL products now
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
+ Complete Pan EU enrollment: Add NL products now
+ Add an of</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Action Required: Website Suppressed ASINs</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Dear Seller,
+We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
+We recommend you to submit the required documents to un-suppress your ASIN and activate your listings.
+Here is a sample of your suppressed ASINs:
+B0F13M1H6F, B0D97JS8WD
+You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
+https://sellercentral.amazon.ca/fixyourproducts/drafts
+To upload the required documents or to appeal in-order to un-suppress the ASINs, please follow this path  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
+ https://sellercentral.amazon.ca/performance/account/health/compliance-request
+If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
+If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory - Action Required</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Dear Weihai US,
+We have recently restricted listings for the product(s) listed below on Amazon.com.
+Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/12/2026), we may dispose of it in accordance with FBA policies.
+Thank you for your attention to this matter.
+Regards,
+Product Safety Team
+Amazon.com
+www.amazon.com
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
+Affected Product(s):
+B0FCDRNTT8
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
+SPC-USAmazon-1917550476493542</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 12317833332] 其他账户问题</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -2668,1956 +4616,10 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>96
- Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
- Hello,
- Starting from April 30, 2026, your Fulfilment by Amazon (FBA) inventory that’s been stored over 270 days (aged), stranded over 60 days or unfulfillable over 14 days will be removed from our UK and EU fulfilment centres to free up capacity in our network.
- If you don’t complete one of the following actions by April 30, 2026, we may automatically dispose, donate, liquidate or return your inventory.
-- For aged inventory (270+ days): Review your at-risk inventory in FBA inventory , then go to Automated fulfillable settings in Seller Central settings and choose a removal option: Disable, return (processing may take up to 90 days) or dispose (liquidation is available for eligible inventory). If you choose Disable, we will not remove your aged inventory.
-- For unfulfillable inventory: Go to Remove unfulfillable inventory and create a removal order.
-- For stranded inventory: Go to Fix stranded inventory and create a removal order or select “Edit automatic action settings” to configure your removal preferences. Note: If you’ve created a return order for FBA inventory in last six months, we’ll att</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-C2S2 PCP Pallet Limited Time Promotion
-Dear Selling Partner,
-Ready to unlock European growth? Join Customs Clearance and Shipping Service (C2S2) PCP Pallets and get an unbeatable launch package: up to €240 in transportation fee reimbursements per shipment during our Spring Promotion (April 10 - June 30, 2026), PLUS 1 year of free Indirect Representation (IR) worth €200, PLUS your first shipment worth €60 completely free.
-It's the perfect time to start shipping cross-border with confidence. Join for free to the PCP-AVASK Pallet solution today.
-[Enroll now with AVASK](https://go.amazonsellerservices.com/e/229492/jfe-form-SV-cA1EXJ0WHz20OFg/7z2qvf2/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-- Automatic tracking: No claims process - we track your shipments automatically
-- Check full [terms and conditions here](https://go.amazonsellerservices.com/e/229492/-C2S2-LTL-Q2-Promotion-TCs-pdf/7z2qvf5/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
-Offer Details:
-Pallets per Shipment                               Your Savings
-1-5 pallets    </t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal and disposal fees to be charged as units are processed</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>96
- FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
- Hello,
- Effective May 1, 2026, Fulfillment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
- This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
- No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
- To review your removal and disposal shipment level charges and when units are removed, go to Transaction view .
- For more information, go to FBA Removal and Disposal fee updates .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon EU S.à r.l.
-38 avenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal and disposal fees to be charged as units are processed</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>96
- FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
- Hello,
- Effective as of May 1, 2026, Fulfilment by Amazon (FBA) removal and disposal fees will be charged on a per-unit basis at the time that each unit is removed or disposed of. This update is in line with industry standards and gives you more visibility into your removal and disposal activities.
- This change only affects when you are charged. The fee rates for removal and disposal fees remain unchanged. Previously, these fees were charged once the entire removal or disposal order was completed.
- No action is required from you. This change will apply automatically to new removal and disposal orders created on or after May 1.
- To review your removal and disposal shipment-level charges and when units are removed, go to Transaction view .
- For more information, go to FBA removal and disposal fee updates .
- The Amazon Europe team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon EU S.à</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Update to FBA item package dimensions</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Update to FBA item package dimensions
- 96
- Starting May 5, 2026, we'll update the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, France, Italy and Spain stores.
-                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA removal request is complete (pVfzD86piw)</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed and shipped your removal
-request (pVfzD86piw) to the address you specified before.
-Return Summary:
-Quantity Requested: 3
-Quantity Successfully Shipped: 3
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being shipped, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-1560397-6680802
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1143494293097040</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (CQhO1/+c38)</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-5850124-1743211
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-650912521107592</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
- votre compte vendeur Amazon</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon Services.
- We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
- Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For details, go to seller Help, and search for “Make a Payment.”
- You can view your payment activity at any time by logging in to your seller account and going to your Payments Report.
- Thank you for selling on Amazon.ca.
- Amazon Services
- *****
- Bonjour d’Amazon Services,
- Nous avons débité votre carte bancaire (Visa) pour CDN$ 44.65 pour le règlement du solde de votre compte vendeur.
- Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (kpCypnMqWe)</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-1188095-0289626
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1372192148348110</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA removal request is complete (UvRxALtvwM)</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed and shipped your removal
-request (UvRxALtvwM) to the address you specified before.
-Return Summary:
-Quantity Requested: 1
-Quantity Successfully Shipped: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being shipped, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-2770073-9467132
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1178678664727600</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID pVfzD86piw
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on April 5, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-1213863031250684</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Reminder: Please share your feedback on MCF</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Reminder: Please share your feedback on MCF
-Dear Weihai US,
-As a valued Multi-Channel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than March 19.
-(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_et9BAqtoDGCsCB8?Q_CHL=gl&amp;amp;Q_DL=EMD_Z45pcIhoS9Jgg2Y_et9BAqtoDGCsCB8_CGC_gVqjuURBQB4eTq0&amp;amp;_g_=g
-This submission form is unique to your Seller account and can only be submitted once.
-DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
-Thank you,
-Your Multi-Channel Fulfillment Team
-This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please vi</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
- votre compte vendeur Amazon</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon Services.
- We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
- Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For details, go to seller Help, and search for “Make a Payment.”
- You can view your payment activity at any time by logging in to your seller account and going to your Payments Report.
- Thank you for selling on Amazon.ca.
- Amazon Services
- *****
- Bonjour d’Amazon Services,
- Nous avons débité votre carte bancaire (Visa) pour CDN$ 44.03 pour le règlement du solde de votre compte vendeur.
- Le montant débité sur votre carte bancaire peut être inférieur au montant total impayé si vous disposez d'une limite de crédit imposée par votre banque. Nous continuerons d'essayer de débiter votre carte bancaire toutes les 24 heures jusqu'à ce que le solde restant de votre compte soit e</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
-On 04/05/26 13:38 PDT, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
- 177.58.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
- Amazon sellers and Amazon Pay merchants can si</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 04/02/26 15:38 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 23,43.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxi</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Amazon Services
- 96
- Review details about your EPR Pay on Behalf reserved amount
- Hello,
- Starting 01-04-2026, we'll hold €501.64 from your payments to cover the eco-contribution fees and Extended Producer Responsibility (EPR) Pay on Behalf service fees for sales of products subject to EPR obligations in our Amazon.es - Amazon.fr store in 2025.
- EPR Pay on Behalf calculates and pays eco-contribution fees for your sales, then debits those amounts from your account. Once fees are charged, any excess reserves will return to your account.
- Our records show you have products listed in the following EPR categories:
- - Do-it-yourself (DIY)
- - Electronical and electrical equipment
- - Packaging
- - Sports
- - Textile
- - Toys
- The amount held back is a combination of two fees:
- Due eco-contribution fees - €299.7
- EPR Pay on Behalf service fees - €201.94
- After 01-04-2026, to review your ASIN-level calculations, reserved amount details, and the reporting period for each EPR category, go to the EPR Pay on Behalf dashboard .
- The reserved amount will be adjusted monthly according to your sales volume. If the reserved amount isn't enough to cover the eco-contributions, we'll charge the additional </t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 03/30/26 15:13 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 133.79.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>View your China tax report for October - December 2025</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>96
- We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
- Hello,
- According to rules for online stores issued by the State Council of China (Decree No. 810), we are required to provide information on China-based sellers to the Chinese tax authority on a quarterly basis.
- We’ve submitted your quarterly tax report covering October to December 2025, which includes your identity information, number of transactions, revenue, and commission and service fees.
- Download your quarterly report (link active for seven days)
-This report is provided for your reference only, no action is required.
- Based on your feedback, we’ve also provided a more granular order-level report that displays your quarterly information by transaction.
- Download your order-level report (link active for seven days)
-Note: Variation between the data in these reports and your payment and Amazon VAT transactions report is expected. Each report uses distinct methodology and serves a different purpose.
- We’ll continue to provide you with quarterly updates on data shared with the Chinese tax authority.
- For more information, go to China tax information reporti</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 03/19/26 15:38 WET, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 74,59.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éxit</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>【请勿回复】
-尊敬的销售合作伙伴，
-《2025/40包装和包装废弃物法规》（PPWR）为所有欧盟国家引入了新要求，旨在使包装更具可持续性、减少废弃物并支持循环经济。相关要求预计于2026年8月12日起正式生效。
-您需要为每个销售包装及包装产品的欧盟成员国，分别获取一个对应国家的EPR包装注册号。包括您已注册“EPR代付服务”的国家。提交有效的包装EPR注册号（ERN）后，您可继续参与EPR代付服务——由我们负责及时完成您在亚马逊店铺销售的环保款项申报、填报及付款。
-【如何完成合规？】
-1. 为简化法国、意大利和西班牙的EPR包装注册流程并协助您完成注册，我们与服务提供商建立了合作，提供具有竞争力的收费方案：
-• 协助您获取法国、意大利和西班牙的包装注册号
-• 代表您担任授权代表（如适用）
-如需 Evat Master/AVASK联系： 请访问 https://sellercentral-europe.amazon.com/gc/epr-compliance/epr-registration-packaging?ref=121_SET_PPWR 根据步骤1提示选择您的服务提供商，通过卖家平台服务中心表单提交您的联系信息。
-注意：填写注册表时，请务必根据提示完整填写您的信息。填写后我们将与服务提供商共享您的业务信息，服务提供商将在72小时内与您联系，提供更多合规服务信息。
-2. 如果您已注册“EPR代付服务”（法国、意大利、西班牙）且拥有有效注册号：您需要将号码上传到亚马逊平台，但上传时您仍然可以选择继续参与代付服务或退出以便自行管理EPR销售申报环保费用。
-如何操作：请访问： https://sellercentral-europe.amazon.com/gc/epr-compliance/epr-registration-packaging?ref=121_SET_PPWR 根据步骤2提示完成选择。
-3. 此外，您也可以通过以下任一途径搜索并选择服务提供商、授权代表完成EPR所有欧盟国家包装法号码注册：
-1) 亚马逊服务商网络：https://spn.globalsellingcommunity.cn/discover
-2) 卖家服务商城： https://sellercentral-europe.amazon.com/service-hub （包装法服务即将上线）。
-更多详细指导，请参考此合规手册：https://m.media-amazon.com/images/G/01/CN_Compliance_Team/PPWR_Compliance_Guidebook.pdf
-如有疑问，请扫码加入亚马逊卖家合规群：
-https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jp</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Address compliance requirements for your listings</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>96
-Action required: Important information about your product listings
- We are contacting you because you have listed products that require you to submit compliance documents.
- Product listings are missing required compliance documents
- Hello,
- We are contacting you because you have listed products that require you to submit compliance documents. Click on Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
- Review Compliance Requirements
- The table below contains a sample of your affected listings. Click on Review Compliance Requirements to see all of your affected listings.
- SKU ASIN Listing Status WH-PW Kit0806 B0DSM44PRS Removed
- Why is this happening?
-This requirement helps to ensure that products are compliant with local laws and safe for customers.
- How do I continue to sell the affected products?
-Click on Review Compliance Requirements to find out more information about the documents you need to provide for each product.
- Was there an error?
-If you believe that you do not need to su</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Live Q&amp;A on customer feedback with experienced sellers</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
-Connect with sellers experienced in customer feedback
-Join us on March 31 for a live Q&amp;A event in the New Seller Community. Experienced Amazon selling partners will answer your customer feedback questions, offering insights from their own journey.
-Before the event, post your toughest questions about managing feedback, buyer-seller messaging, and customer relations.
-[Post your question](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
-[An Amazon delivery driver walks next to an Amazon Prime delivery van.](https://go.amazonsellerservices.com/e/229492/71-ref--spc-em-na-frm-20260324/7z2bw3v/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
-Meet our hosts
-[A checkmark icon]
-Amazon Seller: TVOI50
-Hi, my name is Tish. We’ve been selling on Amazon for 5 years in the Office Furniture category. We are FBM, an authorized re-seller for a major furniture manufacturer and strive to make every transaction a seamless one. If it’s not, our customer</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
-We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0FCDRNTT8, B0D7SKQ6GC
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.com/fixyourproducts/drafts
-To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
-https://sellercentral.amazon.com/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
-We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0D7SKQ6GC, B0FCDRNTT8
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.com/fixyourproducts/drafts
-To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
-https://sellercentral.amazon.com/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
-We recommend you submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0D7SKQ6GC, B0FCDRNTT8
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.com/fixyourproducts/drafts
-To upload the required documents or to appeal to un-suppressed an ASIN, please follow these instructions  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
-https://sellercentral.amazon.com/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/20/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FD8VC559
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1161086478880000</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Submit UK import details by 21/05/2026 to avoid shipping
- restrictions</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit UK import details by 21/05/2026 to avoid shipping restrictions
- Hello Weihai EU,
- Your Amazon.co.uk seller account requires Import Entry Numbers (IENs) for shipments to UK fulfilment centres. You must provide these details by 21/05/2026 to continue creating new UK shipments.
- Why is this happening?
- We are taking this action because we identified shipments to Amazon UK fulfilment centres without valid Import Entry Numbers (IENs). UK Customs authorities assign these IENs when goods are imported into the UK. As the seller, you must obtain these numbers from your customs declarant, logistics agent or freight forwarder to maintain UK shipping compliance .
- Where do I enter my Import Entry Numbers (IEN)?
- To enter the IENs for your applicable shipments:
-- Go to your Shipping Queue and identify shipments received in Amazon UK FCs.
-- Under “Status”, click the “Import details” text. It will open a pop-up, where you can enter the IENs corresponding to the relevant shipment. You must provide a valid IEN.
-- Save your IEN entry.
- If you would need to update your IEN, you can follow the above steps again.
- What happens if I don’t submit these details?
- You have 60 days after first re</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Add products to Amazon.nl for Pan EU eligibility</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Add products to Amazon.nl for Pan EU eligibility 96
- Complete Pan EU enrollment: Add NL products now
-                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
- Complete Pan EU enrollment: Add NL products now
- Add an of</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Action Required: Website Suppressed ASINs</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
-We recommend you to submit the required documents to un-suppress your ASIN and activate your listings.
-Here is a sample of your suppressed ASINs:
-B0F13M1H6F, B0D97JS8WD
-You can download the full list of your suppressed ASINs from the following path “Catalog” &gt;&gt; “Complete your drafts” &gt;&gt; “Completed with Issues” &gt;&gt; “Detail page removed”
-https://sellercentral.amazon.ca/fixyourproducts/drafts
-To upload the required documents or to appeal in-order to un-suppress the ASINs, please follow this path  login to your seller central account and go to “Performance” &gt;&gt; “Account Health”&gt;&gt; “Documentation Requests” under “Product Compliance request” on the right below corner &gt;&gt; “Provide documents” and choose to upload documents or to appeal.
- https://sellercentral.amazon.ca/performance/account/health/compliance-request
-If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-If you are not the correct point of contact, please re-direct this email to the correct point of contact</t>
-        </is>
-      </c>
-    </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4632,231 +4634,21 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
+          <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
+          <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 04/12/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FCDRNTT8
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1917550476493542</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的卖家：
-我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
-① 提交TRF（务必在确认好合作的TIC或进行第二步之前完成，并确保TRF ID成功生成）
-• 登录卖家平台，进入【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】，找到需处理ASIN
-• 点击右侧【提交】，选定TIC服务提供商后点击【继续】提交TRF，完成可在页面查看TRF ID。
-② 向TIC服务提供商支付费用；
-③ 向TIC服务提供商寄送产品样品或提交您已有的外部检测报告或合规文件。
-④ 确保TIC服务商将TRF状态更新为【正在验证】
-如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新”&gt;“验证您的商品”
-⚠️请注意：
-① 同一ASIN可能只在部分欧洲站点被触发通知，若您计划在欧洲（英国及欧盟）继续销售，只需为每个ASIN任选一个站点完成合规，测试结果将同步至全欧站点。
-② 由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。
-③ 如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
-感谢您的支持，祝您合规大卖
-如有疑问，请扫码加入亚马逊卖家合规群：
-https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jpg
-Amazon Global Selling Seller Compliance Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的卖家：
-我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
-① 提交TRF（务必在确认好合作的TIC或进行第二步之前完成，并确保TRF ID成功生成）
-• 登录卖家平台，进入【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】，找到需处理ASIN
-• 点击右侧【提交】，选定TIC服务提供商后点击【继续】提交TRF，完成可在页面查看TRF ID。
-② 向TIC服务提供商支付费用；
-③ 向TIC服务提供商寄送产品样品或提交您已有的外部检测报告或合规文件。
-④ 确保TIC服务商将TRF状态更新为【正在验证】
-如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新”&gt;“验证您的商品”
-⚠️请注意：
-①如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
-②由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。
-感谢您的支持，祝您合规大卖!
-如有疑问，请扫码加入亚马逊卖家合规群：
-https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_sw.jpg
-To contact us again about this issue, please use the Contact Us form in Seller Central using the following link:
-https://sellercentral.amazon.com/cu/case-dashboard/view-case?caseID=18425733131
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -4868,39 +4660,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -4910,39 +4702,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -4952,39 +4744,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -5014,39 +4806,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -5064,39 +4856,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5113,39 +4905,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -5161,39 +4953,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -5222,39 +5014,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -5275,39 +5067,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5322,39 +5114,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5368,40 +5160,40 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5417,39 +5209,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5465,39 +5257,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5513,39 +5305,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5561,40 +5353,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5610,39 +5402,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5660,39 +5452,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -5708,39 +5500,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5755,39 +5547,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -5802,39 +5594,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5855,40 +5647,40 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -5903,39 +5695,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -5956,39 +5748,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -6021,39 +5813,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6069,39 +5861,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6117,39 +5909,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6167,39 +5959,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6216,39 +6008,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -6272,39 +6064,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6319,39 +6111,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -6367,39 +6159,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -6416,40 +6208,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6465,91 +6257,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>96
-Amazon UAE
- Amazon Announcement
- Hello,
- We previously communicated that Fulfillment by Amazon (FBA) removal fees would be introduced in the UAE and Saudi Arabia on March 30, 2026.
-Due to the developing situation in the Middle East, we will not apply FBA removal fees in UAE and Saudi Arabia until further notice . No fees will apply for FBA removal orders initiated by you or Amazon.
-We will notify you of any future change to this policy in advance.
-The Amazon Services team
-- .
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-EUAmazon-1794404611296645</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6570,39 +6310,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6625,39 +6365,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6678,39 +6418,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6734,39 +6474,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6789,148 +6529,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- rJ8tXXz1/k
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-03-26</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-03-26 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRCF83VZ Quantity: 1
-- FNSKU: X002C14R1B Quantity: 1
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillab</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -6948,39 +6579,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7010,39 +6641,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7058,39 +6689,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7106,40 +6737,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7158,40 +6789,40 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
